--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/VIRGINIA_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/VIRGINIA_2012.xlsx
@@ -517,7 +517,7 @@
         <v>5</v>
       </c>
       <c r="D9">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         <v>5</v>
       </c>
       <c r="D39">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="40">
@@ -1345,7 +1345,7 @@
         <v>5</v>
       </c>
       <c r="D55">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="56">
@@ -1777,7 +1777,7 @@
         <v>5</v>
       </c>
       <c r="D79">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="80">
@@ -2749,7 +2749,7 @@
         <v>5</v>
       </c>
       <c r="D133">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="134">
@@ -2803,7 +2803,7 @@
         <v>5</v>
       </c>
       <c r="D136">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="137">
@@ -2839,7 +2839,7 @@
         <v>5</v>
       </c>
       <c r="D138">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="139">
@@ -2947,7 +2947,7 @@
         <v>5</v>
       </c>
       <c r="D144">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="145">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C149">
@@ -3505,7 +3505,7 @@
         <v>5</v>
       </c>
       <c r="D175">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="176">
@@ -3613,7 +3613,7 @@
         <v>5</v>
       </c>
       <c r="D181">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="182">
@@ -3667,7 +3667,7 @@
         <v>5</v>
       </c>
       <c r="D184">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="185">
@@ -3793,7 +3793,7 @@
         <v>5</v>
       </c>
       <c r="D191">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="192">
@@ -3865,7 +3865,7 @@
         <v>5</v>
       </c>
       <c r="D195">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="196">
@@ -3955,7 +3955,7 @@
         <v>5</v>
       </c>
       <c r="D200">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="201">
@@ -4009,7 +4009,7 @@
         <v>5</v>
       </c>
       <c r="D203">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="204">
@@ -4045,7 +4045,7 @@
         <v>5</v>
       </c>
       <c r="D205">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="206">
@@ -4585,7 +4585,7 @@
         <v>5</v>
       </c>
       <c r="D235">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="236">
@@ -4909,7 +4909,7 @@
         <v>5</v>
       </c>
       <c r="D253">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="254">
@@ -4963,7 +4963,7 @@
         <v>5</v>
       </c>
       <c r="D256">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="257">
@@ -5089,7 +5089,7 @@
         <v>5</v>
       </c>
       <c r="D263">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="264">
@@ -6709,7 +6709,7 @@
         <v>5</v>
       </c>
       <c r="D353">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="354">
@@ -6817,7 +6817,7 @@
         <v>5</v>
       </c>
       <c r="D359">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="360">
@@ -6853,7 +6853,7 @@
         <v>5</v>
       </c>
       <c r="D361">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="362">
@@ -7069,7 +7069,7 @@
         <v>5</v>
       </c>
       <c r="D373">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="374">
@@ -7087,7 +7087,7 @@
         <v>5</v>
       </c>
       <c r="D374">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="375">
@@ -7465,7 +7465,7 @@
         <v>5</v>
       </c>
       <c r="D395">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="396">
@@ -8131,7 +8131,7 @@
         <v>5</v>
       </c>
       <c r="D432">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="433">
@@ -8149,7 +8149,7 @@
         <v>5</v>
       </c>
       <c r="D433">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="434">
@@ -8851,7 +8851,7 @@
         <v>5</v>
       </c>
       <c r="D472">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="473">
@@ -8923,7 +8923,7 @@
         <v>5</v>
       </c>
       <c r="D476">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="477">
@@ -8977,7 +8977,7 @@
         <v>5</v>
       </c>
       <c r="D479">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="480">
@@ -9211,7 +9211,7 @@
         <v>5</v>
       </c>
       <c r="D492">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="493">
@@ -9654,14 +9654,14 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C517">
         <v>5</v>
       </c>
       <c r="D517">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="518">
@@ -10291,7 +10291,7 @@
         <v>5</v>
       </c>
       <c r="D552">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="553">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C600">
@@ -11209,7 +11209,7 @@
         <v>5</v>
       </c>
       <c r="D603">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="604">
@@ -11857,7 +11857,7 @@
         <v>5</v>
       </c>
       <c r="D639">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="640">
@@ -11893,7 +11893,7 @@
         <v>5</v>
       </c>
       <c r="D641">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="642">
@@ -12235,7 +12235,7 @@
         <v>5</v>
       </c>
       <c r="D660">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="661">
@@ -12343,7 +12343,7 @@
         <v>5</v>
       </c>
       <c r="D666">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="667">
@@ -12523,7 +12523,7 @@
         <v>5</v>
       </c>
       <c r="D676">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="677">
@@ -12559,7 +12559,7 @@
         <v>5</v>
       </c>
       <c r="D678">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="679">
@@ -12739,7 +12739,7 @@
         <v>5</v>
       </c>
       <c r="D688">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="689">
@@ -12847,7 +12847,7 @@
         <v>5</v>
       </c>
       <c r="D694">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="695">
@@ -13441,7 +13441,7 @@
         <v>5</v>
       </c>
       <c r="D727">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="728">
@@ -13459,7 +13459,7 @@
         <v>5</v>
       </c>
       <c r="D728">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="729">
@@ -14125,7 +14125,7 @@
         <v>5</v>
       </c>
       <c r="D765">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="766">
@@ -14359,7 +14359,7 @@
         <v>5</v>
       </c>
       <c r="D778">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="779">
@@ -14485,7 +14485,7 @@
         <v>5</v>
       </c>
       <c r="D785">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="786">
@@ -14755,7 +14755,7 @@
         <v>5</v>
       </c>
       <c r="D800">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="801">
@@ -15349,7 +15349,7 @@
         <v>5</v>
       </c>
       <c r="D833">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="834">
@@ -15529,7 +15529,7 @@
         <v>5</v>
       </c>
       <c r="D843">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="844">
@@ -15583,7 +15583,7 @@
         <v>5</v>
       </c>
       <c r="D846">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="847">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C894">
@@ -16483,7 +16483,7 @@
         <v>5</v>
       </c>
       <c r="D896">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="897">
@@ -19147,7 +19147,7 @@
         <v>5</v>
       </c>
       <c r="D1044">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="1045">
@@ -19327,7 +19327,7 @@
         <v>5</v>
       </c>
       <c r="D1054">
-        <v>0.000932140193885</v>
+        <v>0.0009321401938850002</v>
       </c>
     </row>
     <row r="1055">
